--- a/exemplos/05 classificaçoes.xlsx
+++ b/exemplos/05 classificaçoes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuno\Desktop\dados rankings\exemplos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuno\Desktop\FM Data\exemplos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FDA117D-37F3-414D-881E-4FA341C725DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD4DBB9-7740-457A-B7F6-E027AD8452B7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Super League" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2902" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="835">
   <si>
     <t>Port City' FC</t>
   </si>
@@ -2307,12 +2307,6 @@
     <t xml:space="preserve">Equipa 1 </t>
   </si>
   <si>
-    <t>Resultado</t>
-  </si>
-  <si>
-    <t>Equipa 2</t>
-  </si>
-  <si>
     <t>Meia Final Equipa 1</t>
   </si>
   <si>
@@ -2337,24 +2331,15 @@
     <t>CAF Challange Cup</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
     <t>Smouha</t>
   </si>
   <si>
     <t>TotalEnergies CAF Confederation Cup</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
     <t>Scotiabank CONCACAF Champions League</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
     <t>Central America Champions League</t>
   </si>
   <si>
@@ -2373,9 +2358,6 @@
     <t>AFC Champions League Elite</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
     <t>Yokohama F･Marinos</t>
   </si>
   <si>
@@ -2421,9 +2403,6 @@
     <t>UEFA European Championship</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
     <t>Países Baixos</t>
   </si>
   <si>
@@ -2433,9 +2412,6 @@
     <t>Ucrânia</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
     <t>País de Gales</t>
   </si>
   <si>
@@ -2505,9 +2481,6 @@
     <t>Taça das Nações Árabes</t>
   </si>
   <si>
-    <t>5-0</t>
-  </si>
-  <si>
     <t>CONCACAF Nations League</t>
   </si>
   <si>
@@ -2517,9 +2490,6 @@
     <t>FIFA Confederation Cup</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
     <t>Ilhas Caimão</t>
   </si>
   <si>
@@ -2559,13 +2529,10 @@
     <t>Competicao</t>
   </si>
   <si>
-    <t>Finalista 1</t>
-  </si>
-  <si>
-    <t>Finalista 2</t>
-  </si>
-  <si>
-    <t>2-3</t>
+    <t>Vencedor</t>
+  </si>
+  <si>
+    <t>Finalista</t>
   </si>
 </sst>
 </file>
@@ -2653,7 +2620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2661,7 +2628,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -44470,440 +44436,428 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B145105-C034-4EBF-8879-58B154EF454A}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>842</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>832</v>
       </c>
       <c r="B1" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="C1" t="s">
+        <v>834</v>
+      </c>
+      <c r="D1" t="s">
         <v>759</v>
       </c>
-      <c r="D1" t="s">
-        <v>844</v>
-      </c>
       <c r="E1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F1" t="s">
         <v>761</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>762</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>763</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>764</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>765</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" t="s">
+        <v>454</v>
+      </c>
+      <c r="G2" t="s">
+        <v>533</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>766</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>767</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="D2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H2" t="s">
-        <v>533</v>
-      </c>
-      <c r="I2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>768</v>
       </c>
       <c r="B3" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>774</v>
+      <c r="C3" t="s">
+        <v>451</v>
       </c>
       <c r="D3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E3" t="s">
-        <v>453</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>1</v>
+        <v>767</v>
       </c>
       <c r="G3" t="s">
-        <v>770</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>226</v>
       </c>
       <c r="I3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>845</v>
-      </c>
-      <c r="D4" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B6" t="s">
         <v>620</v>
       </c>
+      <c r="C6" t="s">
+        <v>199</v>
+      </c>
       <c r="D6" t="s">
-        <v>199</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
-        <v>466</v>
-      </c>
-      <c r="F6" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B7" t="s">
         <v>201</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="B9" t="s">
         <v>115</v>
       </c>
+      <c r="C9" t="s">
+        <v>240</v>
+      </c>
       <c r="D9" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G9" t="s">
-        <v>124</v>
+        <v>242</v>
       </c>
       <c r="H9" t="s">
-        <v>242</v>
+        <v>117</v>
       </c>
       <c r="I9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B10" t="s">
         <v>117</v>
       </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="H10" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B11" t="s">
-        <v>779</v>
+        <v>774</v>
+      </c>
+      <c r="C11" t="s">
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>488</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
+      <c r="C13" t="s">
+        <v>776</v>
+      </c>
       <c r="D13" t="s">
-        <v>782</v>
+        <v>222</v>
       </c>
       <c r="E13" t="s">
-        <v>222</v>
+        <v>436</v>
       </c>
       <c r="F13" t="s">
-        <v>436</v>
+        <v>227</v>
       </c>
       <c r="G13" t="s">
-        <v>227</v>
+        <v>777</v>
       </c>
       <c r="H13" t="s">
-        <v>783</v>
+        <v>185</v>
       </c>
       <c r="I13" t="s">
-        <v>185</v>
-      </c>
-      <c r="J13" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B14" t="s">
         <v>529</v>
       </c>
-      <c r="D14" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="B16" t="s">
         <v>353</v>
       </c>
+      <c r="C16" t="s">
+        <v>252</v>
+      </c>
       <c r="D16" t="s">
-        <v>252</v>
+        <v>497</v>
       </c>
       <c r="E16" t="s">
-        <v>497</v>
+        <v>402</v>
       </c>
       <c r="F16" t="s">
-        <v>402</v>
+        <v>494</v>
       </c>
       <c r="G16" t="s">
-        <v>494</v>
+        <v>251</v>
       </c>
       <c r="H16" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="I16" t="s">
-        <v>256</v>
-      </c>
-      <c r="J16" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="B17" t="s">
         <v>359</v>
       </c>
+      <c r="C17" t="s">
+        <v>782</v>
+      </c>
       <c r="D17" t="s">
-        <v>788</v>
+        <v>411</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>496</v>
       </c>
       <c r="G17" t="s">
-        <v>496</v>
+        <v>407</v>
       </c>
       <c r="H17" t="s">
-        <v>407</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="B18" t="s">
         <v>406</v>
       </c>
+      <c r="C18" t="s">
+        <v>135</v>
+      </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>498</v>
       </c>
       <c r="E18" t="s">
-        <v>498</v>
+        <v>317</v>
       </c>
       <c r="F18" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G18" t="s">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="H18" t="s">
-        <v>270</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s">
-        <v>84</v>
-      </c>
-      <c r="J18" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
+      <c r="C19" t="s">
+        <v>785</v>
+      </c>
       <c r="D19" t="s">
-        <v>791</v>
+        <v>351</v>
       </c>
       <c r="E19" t="s">
-        <v>351</v>
+        <v>263</v>
       </c>
       <c r="F19" t="s">
-        <v>263</v>
+        <v>366</v>
       </c>
       <c r="G19" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H19" t="s">
-        <v>361</v>
+        <v>506</v>
       </c>
       <c r="I19" t="s">
-        <v>506</v>
-      </c>
-      <c r="J19" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="B20" t="s">
         <v>263</v>
       </c>
-      <c r="D20" t="s">
+      <c r="C20" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
       </c>
-      <c r="D21" t="s">
+      <c r="C21" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="B23" t="s">
         <v>402</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C23" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="B24" t="s">
         <v>353</v>
       </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>388</v>
       </c>
       <c r="E24" t="s">
-        <v>388</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>494</v>
       </c>
       <c r="G24" t="s">
-        <v>494</v>
+        <v>286</v>
       </c>
       <c r="H24" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="I24" t="s">
-        <v>441</v>
-      </c>
-      <c r="J24" t="s">
         <v>620</v>
       </c>
     </row>
@@ -44915,367 +44869,295 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9843F1A1-2203-4573-AE68-D8EF5A930295}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>842</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>832</v>
       </c>
       <c r="B1" t="s">
         <v>758</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>759</v>
+      <c r="C1" t="s">
+        <v>833</v>
       </c>
       <c r="D1" t="s">
+        <v>834</v>
+      </c>
+      <c r="E1" t="s">
         <v>760</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>761</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>762</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>763</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>764</v>
       </c>
-      <c r="I1" t="s">
-        <v>765</v>
-      </c>
-      <c r="J1" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="B2" t="s">
         <v>287</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>791</v>
+      </c>
+      <c r="F2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" t="s">
+        <v>352</v>
+      </c>
+      <c r="I2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B3" t="s">
+        <v>793</v>
+      </c>
+      <c r="C3" t="s">
+        <v>794</v>
+      </c>
+      <c r="D3" t="s">
+        <v>795</v>
+      </c>
+      <c r="E3" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>797</v>
       </c>
-      <c r="D2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B5" t="s">
         <v>798</v>
       </c>
-      <c r="G2" t="s">
-        <v>472</v>
-      </c>
-      <c r="H2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I2" t="s">
-        <v>352</v>
-      </c>
-      <c r="J2" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
         <v>799</v>
       </c>
-      <c r="B3" t="s">
+      <c r="G5" t="s">
         <v>800</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="H5" t="s">
         <v>801</v>
       </c>
-      <c r="D3" t="s">
+      <c r="I5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>802</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B7" t="s">
         <v>803</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C7" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" t="s">
         <v>805</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>806</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="D5" t="s">
-        <v>610</v>
-      </c>
-      <c r="E5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="B8" t="s">
         <v>807</v>
       </c>
-      <c r="H5" t="s">
+      <c r="C8" t="s">
         <v>808</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>809</v>
-      </c>
-      <c r="J5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>810</v>
-      </c>
-      <c r="B7" t="s">
-        <v>811</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D7" t="s">
-        <v>812</v>
-      </c>
-      <c r="E7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>814</v>
-      </c>
-      <c r="B8" t="s">
-        <v>815</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="D8" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>817</v>
       </c>
       <c r="B10" t="s">
         <v>433</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>801</v>
+      <c r="C10" t="s">
+        <v>810</v>
       </c>
       <c r="D10" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E10" t="s">
-        <v>819</v>
+        <v>387</v>
       </c>
       <c r="F10" t="s">
-        <v>387</v>
-      </c>
-      <c r="G10" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B11" t="s">
-        <v>822</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D11" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>814</v>
+      </c>
+      <c r="C11" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="B12" t="s">
         <v>220</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="B14" t="s">
-        <v>806</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="D14" t="s">
+        <v>798</v>
+      </c>
+      <c r="C14" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="B16" t="s">
         <v>433</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>781</v>
+      <c r="C16" t="s">
+        <v>805</v>
       </c>
       <c r="D16" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="E16" t="s">
-        <v>812</v>
-      </c>
-      <c r="F16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="B17" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>829</v>
+      <c r="C17" t="s">
+        <v>820</v>
       </c>
       <c r="D17" t="s">
-        <v>830</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="B19" t="s">
-        <v>832</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>774</v>
+        <v>822</v>
+      </c>
+      <c r="C19" t="s">
+        <v>823</v>
       </c>
       <c r="D19" t="s">
-        <v>833</v>
+        <v>805</v>
       </c>
       <c r="E19" t="s">
-        <v>813</v>
-      </c>
-      <c r="F19" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="B20" t="s">
-        <v>830</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>769</v>
+        <v>820</v>
+      </c>
+      <c r="C20" t="s">
+        <v>826</v>
       </c>
       <c r="D20" t="s">
-        <v>836</v>
+        <v>156</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
-      </c>
-      <c r="F20" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="B21" t="s">
         <v>387</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>769</v>
+      <c r="C21" t="s">
+        <v>828</v>
       </c>
       <c r="D21" t="s">
-        <v>838</v>
+        <v>184</v>
       </c>
       <c r="E21" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>769</v>
+      <c r="C22" t="s">
+        <v>831</v>
       </c>
       <c r="D22" t="s">
-        <v>841</v>
+        <v>287</v>
       </c>
       <c r="E22" t="s">
-        <v>287</v>
-      </c>
-      <c r="F22" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
